--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_VIRTUS BOLOGNA.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_VIRTUS BOLOGNA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>38.8408</v>
+        <v>30.6635</v>
       </c>
       <c r="E2" t="n">
-        <v>36.5884</v>
+        <v>31.0645</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2525</v>
+        <v>-0.4014999999999997</v>
       </c>
       <c r="G2" t="n">
-        <v>15.817</v>
+        <v>8.2342</v>
       </c>
       <c r="H2" t="n">
-        <v>11.9046</v>
+        <v>12.3187</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9125</v>
+        <v>-4.084199999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>51.3366</v>
+        <v>33.5851</v>
       </c>
       <c r="K2" t="n">
-        <v>33.6672</v>
+        <v>27.3679</v>
       </c>
       <c r="L2" t="n">
-        <v>17.6692</v>
+        <v>6.217399999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-35.5197</v>
+        <v>-25.3507</v>
       </c>
       <c r="N2" t="n">
-        <v>-21.7629</v>
+        <v>-15.0491</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.7571</v>
+        <v>-10.3018</v>
       </c>
       <c r="P2" t="n">
-        <v>-8.118399999999999</v>
+        <v>-13.2212</v>
       </c>
       <c r="Q2" t="n">
-        <v>-67.4984</v>
+        <v>-61.0035</v>
       </c>
       <c r="R2" t="n">
-        <v>59.3802</v>
+        <v>47.7825</v>
       </c>
       <c r="S2" t="n">
-        <v>35.5861</v>
+        <v>-10.0603</v>
       </c>
       <c r="T2" t="n">
-        <v>31.0707</v>
+        <v>-5.4062</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5158</v>
+        <v>-4.654000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.444</v>
+        <v>45.7103</v>
       </c>
       <c r="W2" t="n">
-        <v>21.6791</v>
+        <v>63.8892</v>
       </c>
       <c r="X2" t="n">
-        <v>-26.123</v>
+        <v>-18.1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>15.496</v>
+        <v>17.2844</v>
       </c>
       <c r="E3" t="n">
-        <v>27.1856</v>
+        <v>16.8506</v>
       </c>
       <c r="F3" t="n">
-        <v>-11.6896</v>
+        <v>0.4339999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>8.7759</v>
+        <v>15.817</v>
       </c>
       <c r="H3" t="n">
-        <v>11.2434</v>
+        <v>11.9046</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.4676</v>
+        <v>3.9125</v>
       </c>
       <c r="J3" t="n">
-        <v>24.5743</v>
+        <v>51.3366</v>
       </c>
       <c r="K3" t="n">
-        <v>18.3544</v>
+        <v>33.6672</v>
       </c>
       <c r="L3" t="n">
-        <v>6.2199</v>
+        <v>17.6692</v>
       </c>
       <c r="M3" t="n">
-        <v>-15.7986</v>
+        <v>-35.5197</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.1105</v>
+        <v>-21.7629</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.6875</v>
+        <v>-13.7571</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0876</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-20.6442</v>
+        <v>-67.4984</v>
       </c>
       <c r="R3" t="n">
-        <v>18.5567</v>
+        <v>59.3802</v>
       </c>
       <c r="S3" t="n">
-        <v>23.1097</v>
+        <v>14.0298</v>
       </c>
       <c r="T3" t="n">
-        <v>19.8033</v>
+        <v>11.3325</v>
       </c>
       <c r="U3" t="n">
-        <v>3.306</v>
+        <v>2.697</v>
       </c>
       <c r="V3" t="n">
-        <v>-14.3018</v>
+        <v>-4.444</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4517</v>
+        <v>21.6791</v>
       </c>
       <c r="X3" t="n">
-        <v>-17.7535</v>
+        <v>-26.123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>13.692</v>
+        <v>11.3211</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4676</v>
+        <v>11.808</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.7755</v>
+        <v>-0.4872999999999996</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5346</v>
+        <v>24.3723</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1919</v>
+        <v>12.2945</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.657999999999999</v>
+        <v>12.0782</v>
       </c>
       <c r="J4" t="n">
-        <v>30.5195</v>
+        <v>57.248</v>
       </c>
       <c r="K4" t="n">
-        <v>17.6375</v>
+        <v>31.0468</v>
       </c>
       <c r="L4" t="n">
-        <v>12.8816</v>
+        <v>26.2015</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.9846</v>
+        <v>-32.8756</v>
       </c>
       <c r="N4" t="n">
-        <v>-9.4452</v>
+        <v>-18.7524</v>
       </c>
       <c r="O4" t="n">
-        <v>-18.5401</v>
+        <v>-14.1231</v>
       </c>
       <c r="P4" t="n">
-        <v>-16.7004</v>
+        <v>-5.7989</v>
       </c>
       <c r="Q4" t="n">
-        <v>-60.0758</v>
+        <v>-55.2047</v>
       </c>
       <c r="R4" t="n">
-        <v>43.3753</v>
+        <v>49.4062</v>
       </c>
       <c r="S4" t="n">
-        <v>27.0384</v>
+        <v>-5.077500000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>24.4944</v>
+        <v>-3.4168</v>
       </c>
       <c r="U4" t="n">
-        <v>2.5442</v>
+        <v>-1.6609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8197</v>
+        <v>-2.1755</v>
       </c>
       <c r="W4" t="n">
-        <v>22.5299</v>
+        <v>13.1811</v>
       </c>
       <c r="X4" t="n">
-        <v>-21.7102</v>
+        <v>-15.3566</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
-        <v>10.8717</v>
+        <v>-0.2131999999999995</v>
       </c>
       <c r="E5" t="n">
-        <v>17.9017</v>
+        <v>14.0066</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.030400000000001</v>
+        <v>-14.2193</v>
       </c>
       <c r="G5" t="n">
-        <v>8.2342</v>
+        <v>8.7759</v>
       </c>
       <c r="H5" t="n">
-        <v>12.3187</v>
+        <v>11.2434</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.084199999999999</v>
+        <v>-2.4676</v>
       </c>
       <c r="J5" t="n">
-        <v>33.5851</v>
+        <v>24.5743</v>
       </c>
       <c r="K5" t="n">
-        <v>27.3679</v>
+        <v>18.3544</v>
       </c>
       <c r="L5" t="n">
-        <v>6.217399999999999</v>
+        <v>6.2199</v>
       </c>
       <c r="M5" t="n">
-        <v>-25.3507</v>
+        <v>-15.7986</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.0491</v>
+        <v>-7.1105</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.3018</v>
+        <v>-8.6875</v>
       </c>
       <c r="P5" t="n">
-        <v>-13.2212</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-61.0035</v>
+        <v>-20.6442</v>
       </c>
       <c r="R5" t="n">
-        <v>47.7825</v>
+        <v>18.5567</v>
       </c>
       <c r="S5" t="n">
-        <v>-29.8515</v>
+        <v>7.4005</v>
       </c>
       <c r="T5" t="n">
-        <v>-18.5694</v>
+        <v>6.6243</v>
       </c>
       <c r="U5" t="n">
-        <v>-11.2824</v>
+        <v>0.7765</v>
       </c>
       <c r="V5" t="n">
-        <v>45.7103</v>
+        <v>-14.3018</v>
       </c>
       <c r="W5" t="n">
-        <v>63.8892</v>
+        <v>3.4517</v>
       </c>
       <c r="X5" t="n">
-        <v>-18.1789</v>
+        <v>-17.7535</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>4.360399999999998</v>
+        <v>-0.6715999999999984</v>
       </c>
       <c r="E6" t="n">
-        <v>10.2414</v>
+        <v>6.0148</v>
       </c>
       <c r="F6" t="n">
-        <v>-5.8811</v>
+        <v>-6.6867</v>
       </c>
       <c r="G6" t="n">
         <v>5.241599999999999</v>
@@ -922,13 +922,13 @@
         <v>19.2525</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3286</v>
+        <v>0.2967000000000003</v>
       </c>
       <c r="T6" t="n">
-        <v>4.1242</v>
+        <v>-0.1028000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2046</v>
+        <v>0.3993999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-15.7198</v>
@@ -955,13 +955,13 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7464999999999997</v>
+        <v>-1.0061</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9009</v>
+        <v>1.4617</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1544</v>
+        <v>-2.4677</v>
       </c>
       <c r="G7" t="n">
         <v>-8.0899</v>
@@ -1000,13 +1000,13 @@
         <v>6.726699999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2821</v>
+        <v>2.5298</v>
       </c>
       <c r="T7" t="n">
-        <v>3.0408</v>
+        <v>1.6016</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2413</v>
+        <v>0.9283</v>
       </c>
       <c r="V7" t="n">
         <v>2.0026</v>
@@ -1033,13 +1033,13 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4818</v>
+        <v>-1.4153</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7234</v>
+        <v>-1.9593</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2415</v>
+        <v>0.544</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3412</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.07599999999999998</v>
+        <v>0.1425</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3181</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.394</v>
+        <v>0.6966</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.879699999999999</v>
+        <v>-3.6941</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04030000000000111</v>
+        <v>-0.5636000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.9205</v>
+        <v>-3.1306</v>
       </c>
       <c r="G9" t="n">
-        <v>24.3723</v>
+        <v>2.5346</v>
       </c>
       <c r="H9" t="n">
-        <v>12.2945</v>
+        <v>8.1919</v>
       </c>
       <c r="I9" t="n">
-        <v>12.0782</v>
+        <v>-5.657999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>57.248</v>
+        <v>30.5195</v>
       </c>
       <c r="K9" t="n">
-        <v>31.0468</v>
+        <v>17.6375</v>
       </c>
       <c r="L9" t="n">
-        <v>26.2015</v>
+        <v>12.8816</v>
       </c>
       <c r="M9" t="n">
-        <v>-32.8756</v>
+        <v>-27.9846</v>
       </c>
       <c r="N9" t="n">
-        <v>-18.7524</v>
+        <v>-9.4452</v>
       </c>
       <c r="O9" t="n">
-        <v>-14.1231</v>
+        <v>-18.5401</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.7989</v>
+        <v>-16.7004</v>
       </c>
       <c r="Q9" t="n">
-        <v>-55.2047</v>
+        <v>-60.0758</v>
       </c>
       <c r="R9" t="n">
-        <v>49.4062</v>
+        <v>43.3753</v>
       </c>
       <c r="S9" t="n">
-        <v>-20.2781</v>
+        <v>9.652099999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-15.184</v>
+        <v>6.4629</v>
       </c>
       <c r="U9" t="n">
-        <v>-5.0938</v>
+        <v>3.1892</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1755</v>
+        <v>0.8197</v>
       </c>
       <c r="W9" t="n">
-        <v>13.1811</v>
+        <v>22.5299</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.3566</v>
+        <v>-21.7102</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BAIOCCHI</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.693</v>
+        <v>-3.8511</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.8919</v>
+        <v>-2.693200000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1989</v>
+        <v>-1.1577</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1531000000000002</v>
+        <v>11.5777</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4895</v>
+        <v>12.2368</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6427000000000002</v>
+        <v>-0.6591</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3862</v>
+        <v>27.6718</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4097000000000001</v>
+        <v>16.0301</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02339999999999998</v>
+        <v>11.6413</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5394000000000001</v>
+        <v>-16.0937</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.07989999999999997</v>
+        <v>-3.7935</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6193</v>
+        <v>-12.3002</v>
       </c>
       <c r="P10" t="n">
-        <v>-4.6391</v>
+        <v>1.6237</v>
       </c>
       <c r="Q10" t="n">
-        <v>-8.118399999999999</v>
+        <v>-34.3292</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4794</v>
+        <v>35.9528</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0626</v>
+        <v>-4.3586</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3873</v>
+        <v>-2.1375</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3246</v>
+        <v>-2.221500000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1444</v>
+        <v>-12.6935</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>6.101100000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1444</v>
+        <v>-18.7946</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. TAYLOR</t>
+          <t>M. BAIOCCHI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.032399999999999</v>
+        <v>-5.8903</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.8787</v>
+        <v>-9.109500000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1535</v>
+        <v>3.2192</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6833</v>
+        <v>0.1531000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6609</v>
+        <v>-0.4895</v>
       </c>
       <c r="I11" t="n">
-        <v>7.3442</v>
+        <v>0.6427000000000002</v>
       </c>
       <c r="J11" t="n">
-        <v>6.9835</v>
+        <v>-0.3862</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1484000000000002</v>
+        <v>-0.4097000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>6.8352</v>
+        <v>0.02339999999999998</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3003</v>
+        <v>0.5394000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.8094</v>
+        <v>-0.07989999999999997</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5088999999999999</v>
+        <v>0.6193</v>
       </c>
       <c r="P11" t="n">
-        <v>-7.4224</v>
+        <v>-4.6391</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.7575</v>
+        <v>-8.118399999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>5.3351</v>
+        <v>3.4794</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.8651</v>
+        <v>0.7399</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.6411</v>
+        <v>-0.6049</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.224</v>
+        <v>1.3449</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.428</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.9641</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>B. TAYLOR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.1397</v>
+        <v>-6.9218</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.0572</v>
+        <v>-6.4631</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0822</v>
+        <v>-0.4585</v>
       </c>
       <c r="G12" t="n">
-        <v>11.5777</v>
+        <v>3.6833</v>
       </c>
       <c r="H12" t="n">
-        <v>12.2368</v>
+        <v>-3.6609</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6591</v>
+        <v>7.3442</v>
       </c>
       <c r="J12" t="n">
-        <v>27.6718</v>
+        <v>6.9835</v>
       </c>
       <c r="K12" t="n">
-        <v>16.0301</v>
+        <v>0.1484000000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>11.6413</v>
+        <v>6.8352</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.0937</v>
+        <v>-3.3003</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.7935</v>
+        <v>-3.8094</v>
       </c>
       <c r="O12" t="n">
-        <v>-12.3002</v>
+        <v>0.5088999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>1.6237</v>
+        <v>-7.4224</v>
       </c>
       <c r="Q12" t="n">
-        <v>-34.3292</v>
+        <v>-12.7575</v>
       </c>
       <c r="R12" t="n">
-        <v>35.9528</v>
+        <v>5.3351</v>
       </c>
       <c r="S12" t="n">
-        <v>-12.6471</v>
+        <v>-0.7547</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.5015</v>
+        <v>-1.2256</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.1463</v>
+        <v>0.4708999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.6935</v>
+        <v>-2.428</v>
       </c>
       <c r="W12" t="n">
-        <v>6.101100000000001</v>
+        <v>0.5361</v>
       </c>
       <c r="X12" t="n">
-        <v>-18.7946</v>
+        <v>-2.9641</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.8796</v>
+        <v>-11.4588</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.353999999999999</v>
+        <v>-12.053</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.526</v>
+        <v>0.5941000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-18.5723</v>
+        <v>-7.485</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.597999999999999</v>
+        <v>-5.9209</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.9742</v>
+        <v>-1.5647</v>
       </c>
       <c r="J13" t="n">
-        <v>14.4607</v>
+        <v>14.1262</v>
       </c>
       <c r="K13" t="n">
-        <v>8.5616</v>
+        <v>1.955</v>
       </c>
       <c r="L13" t="n">
-        <v>5.899100000000001</v>
+        <v>12.1711</v>
       </c>
       <c r="M13" t="n">
-        <v>-33.0327</v>
+        <v>-21.6117</v>
       </c>
       <c r="N13" t="n">
-        <v>-18.1597</v>
+        <v>-7.8761</v>
       </c>
       <c r="O13" t="n">
-        <v>-14.8733</v>
+        <v>-13.7354</v>
       </c>
       <c r="P13" t="n">
-        <v>6.031</v>
+        <v>-0.2318000000000007</v>
       </c>
       <c r="Q13" t="n">
-        <v>-31.314</v>
+        <v>-34.7933</v>
       </c>
       <c r="R13" t="n">
-        <v>37.3449</v>
+        <v>34.5616</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5879999999999997</v>
+        <v>2.3285</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.141600000000001</v>
+        <v>0.1158999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5529999999999997</v>
+        <v>2.2127</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7501</v>
+        <v>-6.07</v>
       </c>
       <c r="W13" t="n">
-        <v>15.6402</v>
+        <v>8.498000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.3903</v>
+        <v>-14.568</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.8041</v>
+        <v>-11.5669</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.5739</v>
+        <v>-6.927099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7701999999999993</v>
+        <v>-4.6397</v>
       </c>
       <c r="G14" t="n">
-        <v>-7.485</v>
+        <v>-23.2589</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.9209</v>
+        <v>-28.0407</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5647</v>
+        <v>4.7814</v>
       </c>
       <c r="J14" t="n">
-        <v>14.1262</v>
+        <v>23.1334</v>
       </c>
       <c r="K14" t="n">
-        <v>1.955</v>
+        <v>-4.1142</v>
       </c>
       <c r="L14" t="n">
-        <v>12.1711</v>
+        <v>27.2484</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.6117</v>
+        <v>-46.3928</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.8761</v>
+        <v>-23.9261</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.7354</v>
+        <v>-22.4669</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2318000000000007</v>
+        <v>3.015499999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-34.7933</v>
+        <v>-56.1328</v>
       </c>
       <c r="R14" t="n">
-        <v>34.5616</v>
+        <v>59.1483</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0162</v>
+        <v>-3.5602</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4054</v>
+        <v>-5.478499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>2.3889</v>
+        <v>1.9191</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.07</v>
+        <v>12.237</v>
       </c>
       <c r="W14" t="n">
-        <v>8.498000000000001</v>
+        <v>31.5503</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.568</v>
+        <v>-19.3133</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-23.3329</v>
+        <v>-15.6936</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.5424</v>
+        <v>-3.2271</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.7906</v>
+        <v>-12.4664</v>
       </c>
       <c r="G15" t="n">
-        <v>-23.2589</v>
+        <v>-18.5723</v>
       </c>
       <c r="H15" t="n">
-        <v>-28.0407</v>
+        <v>-9.597999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>4.7814</v>
+        <v>-8.9742</v>
       </c>
       <c r="J15" t="n">
-        <v>23.1334</v>
+        <v>14.4607</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.1142</v>
+        <v>8.5616</v>
       </c>
       <c r="L15" t="n">
-        <v>27.2484</v>
+        <v>5.899100000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-46.3928</v>
+        <v>-33.0327</v>
       </c>
       <c r="N15" t="n">
-        <v>-23.9261</v>
+        <v>-18.1597</v>
       </c>
       <c r="O15" t="n">
-        <v>-22.4669</v>
+        <v>-14.8733</v>
       </c>
       <c r="P15" t="n">
-        <v>3.015499999999999</v>
+        <v>6.031</v>
       </c>
       <c r="Q15" t="n">
-        <v>-56.1328</v>
+        <v>-31.314</v>
       </c>
       <c r="R15" t="n">
-        <v>59.1483</v>
+        <v>37.3449</v>
       </c>
       <c r="S15" t="n">
-        <v>-15.3261</v>
+        <v>-1.4022</v>
       </c>
       <c r="T15" t="n">
-        <v>-13.094</v>
+        <v>-2.0146</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.2323</v>
+        <v>0.6124999999999998</v>
       </c>
       <c r="V15" t="n">
-        <v>12.237</v>
+        <v>-1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>31.5503</v>
+        <v>15.6402</v>
       </c>
       <c r="X15" t="n">
-        <v>-19.3133</v>
+        <v>-17.3903</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>-35.7162</v>
+        <v>-27.9891</v>
       </c>
       <c r="E16" t="n">
-        <v>-27.5177</v>
+        <v>-24.1565</v>
       </c>
       <c r="F16" t="n">
-        <v>-8.198700000000001</v>
+        <v>-3.832699999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-25.5142</v>
@@ -1702,13 +1702,13 @@
         <v>52.8855</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.7222</v>
+        <v>0.005000000000000226</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.063800000000001</v>
+        <v>-0.7024000000000002</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.6589</v>
+        <v>0.7069999999999996</v>
       </c>
       <c r="V16" t="n">
         <v>-9.9023</v>
@@ -1735,13 +1735,13 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>-133.1173</v>
+        <v>-106.4662</v>
       </c>
       <c r="E17" t="n">
-        <v>-114.6609</v>
+        <v>-94.2321</v>
       </c>
       <c r="F17" t="n">
-        <v>-18.4564</v>
+        <v>-12.234</v>
       </c>
       <c r="G17" t="n">
         <v>-71.35169999999999</v>
@@ -1780,13 +1780,13 @@
         <v>62.1635</v>
       </c>
       <c r="S17" t="n">
-        <v>-29.6806</v>
+        <v>-3.0291</v>
       </c>
       <c r="T17" t="n">
-        <v>-25.1274</v>
+        <v>-4.6985</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.553299999999999</v>
+        <v>1.6695</v>
       </c>
       <c r="V17" t="n">
         <v>17.7846</v>
@@ -1813,13 +1813,13 @@
         <v>38</v>
       </c>
       <c r="D18" t="n">
-        <v>-173.0693</v>
+        <v>-137.5691</v>
       </c>
       <c r="E18" t="n">
-        <v>-92.87419999999997</v>
+        <v>-80.17830000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-80.19579999999999</v>
+        <v>-57.3908</v>
       </c>
       <c r="G18" t="n">
         <v>-75.2235</v>
@@ -1858,16 +1858,16 @@
         <v>536.9748999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-26.61660000000001</v>
+        <v>8.882199999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-12.90020000000001</v>
+        <v>-0.2045000000000012</v>
       </c>
       <c r="U18" t="n">
-        <v>-13.7186</v>
+        <v>9.087199999999998</v>
       </c>
       <c r="V18" t="n">
-        <v>5.316500000000001</v>
+        <v>5.316500000000006</v>
       </c>
       <c r="W18" t="n">
         <v>236.8618</v>
